--- a/dollarexpress/resources/sample/dollarexpress/dollarExpressWinShow.xlsx
+++ b/dollarexpress/resources/sample/dollarexpress/dollarExpressWinShow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\dollarexpress\resources\sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\dollarexpress\resources\sample\dollarexpress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7975901F-3EF2-4342-B8DD-E7FD923D502F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1429650B-6F34-48F9-AAF0-7B0E830222B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -642,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="14.875" customWidth="1"/>
@@ -687,57 +687,61 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>500</v>
-      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>5000</v>
       </c>
     </row>
